--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.98843858966013</v>
+        <v>3.248121270819771</v>
       </c>
       <c r="D2" t="n">
-        <v>49.04511175313631</v>
+        <v>7.969830659884651</v>
       </c>
       <c r="E2" t="n">
-        <v>7.581736486812488</v>
+        <v>1.232032179107029</v>
       </c>
       <c r="F2" t="n">
-        <v>9.957558407226351</v>
+        <v>1.618103241174282</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.82536846808489</v>
+        <v>1.759122376063794</v>
       </c>
       <c r="D3" t="n">
-        <v>16.4871874545187</v>
+        <v>2.67916796135929</v>
       </c>
       <c r="E3" t="n">
-        <v>7.581736486812488</v>
+        <v>1.232032179107029</v>
       </c>
       <c r="F3" t="n">
-        <v>9.957558407226351</v>
+        <v>1.618103241174282</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.19399571909602</v>
+        <v>3.606524304353103</v>
       </c>
       <c r="D4" t="n">
-        <v>21.84125293186444</v>
+        <v>3.549203601427972</v>
       </c>
       <c r="E4" t="n">
-        <v>7.581736486812488</v>
+        <v>1.232032179107029</v>
       </c>
       <c r="F4" t="n">
-        <v>9.957558407226351</v>
+        <v>1.618103241174282</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.24996768194439</v>
+        <v>6.703119748315964</v>
       </c>
       <c r="D5" t="n">
-        <v>40.6658698634683</v>
+        <v>6.608203852813599</v>
       </c>
       <c r="E5" t="n">
-        <v>7.581736486812488</v>
+        <v>1.232032179107029</v>
       </c>
       <c r="F5" t="n">
-        <v>9.957558407226351</v>
+        <v>1.618103241174282</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.14963873937738</v>
+        <v>3.761816295148824</v>
       </c>
       <c r="D6" t="n">
-        <v>39.36258668012649</v>
+        <v>6.396420335520555</v>
       </c>
       <c r="E6" t="n">
-        <v>7.581736486812488</v>
+        <v>1.232032179107029</v>
       </c>
       <c r="F6" t="n">
-        <v>9.957558407226351</v>
+        <v>1.618103241174282</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.6886104551383</v>
+        <v>3.199399198959974</v>
       </c>
       <c r="D7" t="n">
-        <v>44.5044214354944</v>
+        <v>7.23196848326784</v>
       </c>
       <c r="E7" t="n">
-        <v>7.581736486812488</v>
+        <v>1.232032179107029</v>
       </c>
       <c r="F7" t="n">
-        <v>9.957558407226351</v>
+        <v>1.618103241174282</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.54434071933937</v>
+        <v>5.775955366892648</v>
       </c>
       <c r="D8" t="n">
-        <v>29.92770762843166</v>
+        <v>4.863252489620145</v>
       </c>
       <c r="E8" t="n">
-        <v>7.581736486812488</v>
+        <v>1.232032179107029</v>
       </c>
       <c r="F8" t="n">
-        <v>9.957558407226351</v>
+        <v>1.618103241174282</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.25978578650665</v>
+        <v>4.104715190307331</v>
       </c>
       <c r="D9" t="n">
-        <v>33.71490906871415</v>
+        <v>5.478672723666049</v>
       </c>
       <c r="E9" t="n">
-        <v>7.581736486812488</v>
+        <v>1.232032179107029</v>
       </c>
       <c r="F9" t="n">
-        <v>9.957558407226351</v>
+        <v>1.618103241174282</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.15392023986904</v>
+        <v>5.06251203897872</v>
       </c>
       <c r="D10" t="n">
-        <v>35.52848294216182</v>
+        <v>5.773378478101296</v>
       </c>
       <c r="E10" t="n">
-        <v>7.581736486812488</v>
+        <v>1.232032179107029</v>
       </c>
       <c r="F10" t="n">
-        <v>9.957558407226351</v>
+        <v>1.618103241174282</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>31.6952391649625</v>
+        <v>5.150476364306406</v>
       </c>
       <c r="D11" t="n">
-        <v>31.8578033032813</v>
+        <v>5.176893036783212</v>
       </c>
       <c r="E11" t="n">
-        <v>7.581736486812488</v>
+        <v>1.232032179107029</v>
       </c>
       <c r="F11" t="n">
-        <v>9.957558407226351</v>
+        <v>1.618103241174282</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12332909443216</v>
+        <v>4.407540977845226</v>
       </c>
       <c r="D12" t="n">
-        <v>44.00965431879211</v>
+        <v>7.151568826803718</v>
       </c>
       <c r="E12" t="n">
-        <v>7.581736486812488</v>
+        <v>1.232032179107029</v>
       </c>
       <c r="F12" t="n">
-        <v>9.957558407226351</v>
+        <v>1.618103241174282</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>28.15463162023865</v>
+        <v>4.575127638288781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.51655465671547</v>
+        <v>2.683940131716264</v>
       </c>
       <c r="E13" t="n">
-        <v>7.581736486812488</v>
+        <v>1.232032179107029</v>
       </c>
       <c r="F13" t="n">
-        <v>9.957558407226351</v>
+        <v>1.618103241174282</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>39.16222149670973</v>
+        <v>6.363860993215332</v>
       </c>
       <c r="D14" t="n">
-        <v>50.75601661059569</v>
+        <v>8.247852699221799</v>
       </c>
       <c r="E14" t="n">
-        <v>7.581736486812488</v>
+        <v>1.232032179107029</v>
       </c>
       <c r="F14" t="n">
-        <v>9.957558407226351</v>
+        <v>1.618103241174282</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12912633593928</v>
+        <v>2.620983029590132</v>
       </c>
       <c r="D15" t="n">
-        <v>28.5668963042013</v>
+        <v>4.642120649432712</v>
       </c>
       <c r="E15" t="n">
-        <v>7.581736486812488</v>
+        <v>1.232032179107029</v>
       </c>
       <c r="F15" t="n">
-        <v>9.957558407226351</v>
+        <v>1.618103241174282</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>26.34522882267443</v>
+        <v>4.281099683684594</v>
       </c>
       <c r="D16" t="n">
-        <v>33.54928812704794</v>
+        <v>5.451759320645291</v>
       </c>
       <c r="E16" t="n">
-        <v>7.581736486812488</v>
+        <v>1.232032179107029</v>
       </c>
       <c r="F16" t="n">
-        <v>9.957558407226351</v>
+        <v>1.618103241174282</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>22.59421778569665</v>
+        <v>3.671560390175705</v>
       </c>
       <c r="D17" t="n">
-        <v>32.32704782896183</v>
+        <v>5.253145272206297</v>
       </c>
       <c r="E17" t="n">
-        <v>7.581736486812488</v>
+        <v>1.232032179107029</v>
       </c>
       <c r="F17" t="n">
-        <v>9.957558407226351</v>
+        <v>1.618103241174282</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>32.40247035728782</v>
+        <v>5.265401433059271</v>
       </c>
       <c r="D18" t="n">
-        <v>38.68156552586857</v>
+        <v>6.285754397953643</v>
       </c>
       <c r="E18" t="n">
-        <v>7.581736486812488</v>
+        <v>1.232032179107029</v>
       </c>
       <c r="F18" t="n">
-        <v>9.957558407226351</v>
+        <v>1.618103241174282</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>26.4585182544843</v>
+        <v>4.299509216353699</v>
       </c>
       <c r="D19" t="n">
-        <v>21.50087605647569</v>
+        <v>3.493892359177299</v>
       </c>
       <c r="E19" t="n">
-        <v>7.581736486812488</v>
+        <v>1.232032179107029</v>
       </c>
       <c r="F19" t="n">
-        <v>9.957558407226351</v>
+        <v>1.618103241174282</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
